--- a/results/job_matches_2026-09-11.xlsx
+++ b/results/job_matches_2026-09-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Data Architect – Databricks</t>
+          <t>Platform &amp; Data Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Google Cloud Platform</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3814c47fcd40bb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=05b8d6e4d98fa228</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Data Integration Engineer</t>
+          <t>Senior Data Engineer / Data Architect – Databricks</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HomeServices of America</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, S3, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dece858441573583</t>
+          <t>https://www.indeed.com/viewjob?jk=3814c47fcd40bb0f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>Sr Data Integration Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>HomeServices of America</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d231c0429c2d5a82</t>
+          <t>https://www.indeed.com/viewjob?jk=dece858441573583</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>(1112754) Senior Software Engineer - Java/AWS Backend</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Diversified Services Network</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f823b2967bc25ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d231c0429c2d5a82</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e5ebe6596fd5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4f823b2967bc25ff</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a2550e31c47b05</t>
+          <t>https://www.indeed.com/viewjob?jk=53e5ebe6596fd5cc</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f454c459d8715c2</t>
+          <t>https://www.indeed.com/viewjob?jk=79a2550e31c47b05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>(1112754) Senior Software Engineer - Java/AWS Backend</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Diversified Services Network</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab311aee9088816</t>
+          <t>https://www.indeed.com/viewjob?jk=9f454c459d8715c2</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=060cda39e6c67619</t>
+          <t>https://www.indeed.com/viewjob?jk=eab311aee9088816</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>(1112164) Senior Software Engineer - Java/AWS</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Diversified Services Network</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e81425a0990a5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=060cda39e6c67619</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b1ca06bddd5e551</t>
+          <t>https://www.indeed.com/viewjob?jk=8e81425a0990a5a5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Morgan WM Java + Python - C1 - Level</t>
+          <t>(1112164) Senior Software Engineer - Java/AWS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Diversified Services Network</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2237bdba45156557</t>
+          <t>https://www.indeed.com/viewjob?jk=8b1ca06bddd5e551</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Senior Site Reliability Engineer - FedRAMP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Hive, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd7cac2745190a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b70689612d7d51ee</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Morgan WM Java + Python - C1 - Level</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,147 +941,147 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b5fdfad3bcb351</t>
+          <t>https://www.indeed.com/viewjob?jk=2237bdba45156557</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f67526f506467e7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5f05e5a352797a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4de186a738732d</t>
+          <t>https://www.indeed.com/viewjob?jk=d705b2d3559bb3c6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9fc3a90bd6ff881</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fca088326cd72d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>Alignment Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5f05e5a352797a</t>
+          <t>https://www.indeed.com/viewjob?jk=27ebfdf981995a91</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Malibu Boats</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Loudon, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, MySQL, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175e6757af0bf2a6</t>
+          <t>https://www.indeed.com/viewjob?jk=215a62808c4ca701</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Developer - Java (POS)</t>
+          <t>Senior Software Engineer – Full Stack / Backend / AI Systems</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,207 +1161,207 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7519e1318081914</t>
+          <t>https://www.indeed.com/viewjob?jk=2ee3d7ccc5b43286</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f528980ed0c8d2a7</t>
+          <t>https://www.indeed.com/viewjob?jk=b88bdbb7db1c1b00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f02dc8343f177b</t>
+          <t>https://www.indeed.com/viewjob?jk=45fd760fc1984df4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3376613ab3f984d6</t>
+          <t>https://www.indeed.com/viewjob?jk=3742efecc003f285</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294751ce2ccb4446</t>
+          <t>https://www.indeed.com/viewjob?jk=e7069af551bc0776</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Data Developer - ETL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ExcelaCom</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41caab3acdd93a76</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8b2e1080230339</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Platform Engineer - Databricks and Cloud</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Finbott</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Azure, Databricks, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a62808c4ca701</t>
+          <t>https://www.indeed.com/viewjob?jk=c7ec1ef182d61019</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Full Stack / Backend / AI Systems</t>
+          <t>Sr. Azure dotNet AI Integration Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Berlin Packaging</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ee3d7ccc5b43286</t>
+          <t>https://www.indeed.com/viewjob?jk=dc29c100a8b89c42</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Application Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
+          <t>S3, RDS, Azure, Scala, Kafka, SQL Server, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88bdbb7db1c1b00</t>
+          <t>https://www.indeed.com/viewjob?jk=b5697b129c567549</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Analytics Engineer 2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
+          <t>AWS, EMR, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45fd760fc1984df4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e7ead749ef677c7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ellucian</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3742efecc003f285</t>
+          <t>https://www.indeed.com/viewjob?jk=a1dae4f6c34916d4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Azure Cloud Solutions Developer / Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Doeren Mayhew CPAs and Advisors</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, SQL Server, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7069af551bc0776</t>
+          <t>https://www.indeed.com/viewjob?jk=f16b1ba2fceeeff4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Developer - ETL</t>
+          <t>Senior Feature Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ExcelaCom</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,102 +1581,102 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8b2e1080230339</t>
+          <t>https://www.indeed.com/viewjob?jk=fc268f2e08eed41b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Amherst, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hive, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12312783d59ed413</t>
+          <t>https://www.indeed.com/viewjob?jk=c40cbadc2d21dbaf</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hive, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ada96da7df4f88d</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f5698c0d5c0c74</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Application Engineer II</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Brooklyn, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Kafka, SQL Server, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5697b129c567549</t>
+          <t>https://www.indeed.com/viewjob?jk=b59e4133cbdb8ecb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcfd83790c152b3</t>
+          <t>https://www.indeed.com/viewjob?jk=301dcda44c4f6fc9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer (contract)</t>
+          <t>Forward Deployed Software Engineer - Equities Technology</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Step Functions, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df4bb06b967bbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ef51fce4a7feef</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Azure dotNet AI Integration Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Berlin Packaging</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Kafka, Oracle</t>
+          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc29c100a8b89c42</t>
+          <t>https://www.indeed.com/viewjob?jk=dd06fb948a236148</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Analytics Engineer 2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ELT, dbt</t>
+          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e7ead749ef677c7</t>
+          <t>https://www.indeed.com/viewjob?jk=3c059719ff1f4a84</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Datawarehouse, Service &amp; Tools</t>
+          <t>Senior Data Engineer, Insights Delivery Merch (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a9723e44861c14</t>
+          <t>https://www.indeed.com/viewjob?jk=e052b75c19429d44</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Azure Cloud Solutions Developer / Engineer</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Doeren Mayhew CPAs and Advisors</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, SQL Server, Power BI, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16b1ba2fceeeff4</t>
+          <t>https://www.indeed.com/viewjob?jk=ce267e690cfe27d7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure Cloud Solutions Architect - Remote in US</t>
+          <t>Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Colaberry</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Scala, MySQL, Azure Cosmos DB, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b410cde48b67dc</t>
+          <t>https://www.indeed.com/viewjob?jk=8afd4daee0cfbd6a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Colaberry</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Amherst, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40cbadc2d21dbaf</t>
+          <t>https://www.indeed.com/viewjob?jk=feb309dc36a3ade0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f5698c0d5c0c74</t>
+          <t>https://www.indeed.com/viewjob?jk=700edad9dfcb975f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brooklyn, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59e4133cbdb8ecb</t>
+          <t>https://www.indeed.com/viewjob?jk=eff7ed7ce6374b3b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>IAM, RDS, BigQuery, Dataflow, Cloud Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301dcda44c4f6fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9545abd3a0f68d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Feature Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc268f2e08eed41b</t>
+          <t>https://www.indeed.com/viewjob?jk=348bb65020d238ec</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce267e690cfe27d7</t>
+          <t>https://www.indeed.com/viewjob?jk=3cb87de2d0210269</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Colaberry</t>
+          <t>VRN Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afd4daee0cfbd6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6a06ecdadb7f76</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Contract)</t>
+          <t>MLOps Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Colaberry</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb309dc36a3ade0</t>
+          <t>https://www.indeed.com/viewjob?jk=6e2aae4eab6d41c6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=456814563675f6cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4f16755404b284eb</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700edad9dfcb975f</t>
+          <t>https://www.indeed.com/viewjob?jk=198a1d32c3c5a248</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198a1d32c3c5a248</t>
+          <t>https://www.indeed.com/viewjob?jk=ab128e3501b51439</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Persistent Systems</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=348bb65020d238ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f12f5f159f8687e2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, GCP, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd45ffb84690ca5d</t>
+          <t>https://www.indeed.com/viewjob?jk=809926ba4c12a008</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Product Engineer (Databricks)</t>
+          <t>Senior Storage Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, MLflow</t>
+          <t>S3, RDS, Scala, Snowflake, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573efb398da27847</t>
+          <t>https://www.indeed.com/viewjob?jk=a41755acf2e74e13</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VRN Technologies</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, Scala, Snowflake</t>
+          <t>RDS, Hadoop, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6a06ecdadb7f76</t>
+          <t>https://www.indeed.com/viewjob?jk=17d4577fc7f8f41d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff7ed7ce6374b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=e60af316cfb20b16</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f16755404b284eb</t>
+          <t>https://www.indeed.com/viewjob?jk=345c319d29f5fb24</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior DevOps engineer.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Ayla Networks</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, Cassandra, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,137 +2561,137 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cb87de2d0210269</t>
+          <t>https://www.indeed.com/viewjob?jk=a77b42dadc3d64bb</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer - Access Management (Java Full Stack)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc88f49ae19c3ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae52bab9bde8833</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab128e3501b51439</t>
+          <t>https://www.indeed.com/viewjob?jk=92ef430c583f0949</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Persistent Systems</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f12f5f159f8687e2</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ef978918551b6c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MLOps Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e2aae4eab6d41c6</t>
+          <t>https://www.indeed.com/viewjob?jk=637d2d6e8ea9d1ef</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Storage Platform Engineer</t>
+          <t>Sr. Cloud Infrastructure &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Ambarella</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,199 +2736,199 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41755acf2e74e13</t>
+          <t>https://www.indeed.com/viewjob?jk=5d92d093b53bf68d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Senior Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a84f1785db094f6</t>
+          <t>https://www.indeed.com/viewjob?jk=564e7d0106f9c065</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Vantive</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, GCP, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809926ba4c12a008</t>
+          <t>https://www.indeed.com/viewjob?jk=4b951826f674481d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform (Partner 16, Partner 18)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e866ca403b7a08</t>
+          <t>https://www.indeed.com/viewjob?jk=c740e2d589eb308c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Factory (Partner 16, Partner 18)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac87d7854fb47ac</t>
+          <t>https://www.indeed.com/viewjob?jk=822b2e4556cf1c5f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer, Systems (Partner 16, Partner 18)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c333cc6dde3f595b</t>
+          <t>https://www.indeed.com/viewjob?jk=ba247d1fc82d579c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d4577fc7f8f41d</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0849ec21c1c08</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60af316cfb20b16</t>
+          <t>https://www.indeed.com/viewjob?jk=a56325de82ab5543</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior DevOps engineer.</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ayla Networks</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, Cassandra, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77b42dadc3d64bb</t>
+          <t>https://www.indeed.com/viewjob?jk=c34fa2d9b2a5c0cf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae52bab9bde8833</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9141d944a31a5a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Cloud Infrastructure &amp; DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ambarella</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d92d093b53bf68d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d833ee1e80654c8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Power BI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564e7d0106f9c065</t>
+          <t>https://www.indeed.com/viewjob?jk=280e75cabd3c6a06</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Junior Full Stack Software Engineer AI and Cloud Applications</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ZincFive</t>
+          <t>Agility Technologies Inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tualatin, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a103bc6ce2d7b66</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2063590dad13da</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Business Analyst - Data Intelligence</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>University of North Carolina at Greensboro</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=241fedf4f4795a9c</t>
+          <t>https://www.indeed.com/viewjob?jk=d035d7c47f5688b5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
+          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Vantive</t>
+          <t>LexisNexis Reed Tech</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Horsham, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b951826f674481d</t>
+          <t>https://www.indeed.com/viewjob?jk=81ef43c8ccb7678a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Horsham, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0463821856273c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=b853a7d928445871</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data engineer- Sr Consultant</t>
+          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Horsham, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f50e943f0e086f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bcb4fe5f29db11</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Architect – Data Analytics (Remote)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ferguson</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, ETL, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Databricks Lakehouse, Power BI, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c740e2d589eb308c</t>
+          <t>https://www.indeed.com/viewjob?jk=25bb148408c57615</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LexisNexis Reed Tech</t>
+          <t>Taxrise</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Horsham, PA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ef43c8ccb7678a</t>
+          <t>https://www.indeed.com/viewjob?jk=4d8be5c844ecb981</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Software Developer Cloud &amp; Distributed Systems</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Taxrise</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Cassandra, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8be5c844ecb981</t>
+          <t>https://www.indeed.com/viewjob?jk=9407487c3afcb12c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hallmark</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d28e6b695048282</t>
+          <t>https://www.indeed.com/viewjob?jk=19d1b36881ddad57</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Solutions Architect – Data Analytics (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Youth Villages</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Databricks Lakehouse, Power BI, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,102 +3471,102 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25bb148408c57615</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8c0277359b3cc2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Crane Aerospace &amp; Electronics</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lynnwood, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Oracle, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfc8b8f48b55687</t>
+          <t>https://www.indeed.com/viewjob?jk=df8e9130941aedc7</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Sr Enterprise Data Platform and Engineering</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Academy Sports + Outdoors</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Katy, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ac97ed953cb74f</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7fe15b0b60a4d2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Horsham, PA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b853a7d928445871</t>
+          <t>https://www.indeed.com/viewjob?jk=f2654e3bd2509e90</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Horsham, PA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,94 +3611,94 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bcb4fe5f29db11</t>
+          <t>https://www.indeed.com/viewjob?jk=1354b65cdd4f0090</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Systems &amp; Solutions Engineer</t>
+          <t>Cloud Engineer II- AWS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BWX Technologies</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Pittsford, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, ELT, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72960e997f8affed</t>
+          <t>https://www.indeed.com/viewjob?jk=cce58f883c3524b4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Application Security Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>REPAY</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Kafka, Oracle, Terraform, Kubernetes, Git</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b145be092bbc45</t>
+          <t>https://www.indeed.com/viewjob?jk=d4be196fbc9a16bc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Data Platform Administration Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Hallmark</t>
+          <t>Wesco</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d1b36881ddad57</t>
+          <t>https://www.indeed.com/viewjob?jk=4d1276474c632f42</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technology Business Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Youth Villages</t>
+          <t>Ochsner Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Jefferson, LA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f8c0277359b3cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=e95b750693e2318f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Architect 5 TX - Enterprise Data &amp; Analytics - FT - Days</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>UC Irvine Health</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, EMR, Athena, RDS, Azure, Databricks, GCP, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2654e3bd2509e90</t>
+          <t>https://www.indeed.com/viewjob?jk=87e85e74388cdd06</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr Enterprise Data Platform and Engineering</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Academy Sports + Outdoors</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Katy, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7fe15b0b60a4d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a0920adba0ab6199</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>Sr Software Engineer Azure &amp; Microsoft Cloud</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Leggett &amp; Platt</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git, Azure Monitor</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1354b65cdd4f0090</t>
+          <t>https://www.indeed.com/viewjob?jk=7bdf03283a9a5d27</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Cloud Engineer II- AWS</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>adonis</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Pittsford, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Git, Bitbucket, Datadog</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3890,216 +3890,6 @@
         </is>
       </c>
       <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cce58f883c3524b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer Azure &amp; Microsoft Cloud</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Leggett &amp; Platt</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Lenexa, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7bdf03283a9a5d27</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Java Microservices</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8e3e233479d613</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Java Microservices</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86a42ca990ed148f</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Samsara</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0920adba0ab6199</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior AWS Integration Developer - Remote US Position</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>McKinney, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, Scala, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28c061b38565c9ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>adonis</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Git, Bitbucket, Datadog</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d5f405cef6030adc</t>
         </is>

--- a/results/job_matches_2026-09-11.xlsx
+++ b/results/job_matches_2026-09-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Morgan WM Java + Python - C1 - Level</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>EIS Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2237bdba45156557</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6ad6527a71b393</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Morgan WM Java + Python - C1 - Level</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5f05e5a352797a</t>
+          <t>https://www.indeed.com/viewjob?jk=2237bdba45156557</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d705b2d3559bb3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5f05e5a352797a</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fca088326cd72d</t>
+          <t>https://www.indeed.com/viewjob?jk=d705b2d3559bb3c6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>GenAI Engineer / Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alignment Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27ebfdf981995a91</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbc2ded1357ab6b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>GenAI Engineer / Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Finbott</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a62808c4ca701</t>
+          <t>https://www.indeed.com/viewjob?jk=7440e02579888544</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Full Stack / Backend / AI Systems</t>
+          <t>AI /ML Data Scientist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ee3d7ccc5b43286</t>
+          <t>https://www.indeed.com/viewjob?jk=386200b3002aff99</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88bdbb7db1c1b00</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fca088326cd72d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>AI /ML Data Scientist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45fd760fc1984df4</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2ed4b81dac13d2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alignment Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3742efecc003f285</t>
+          <t>https://www.indeed.com/viewjob?jk=27ebfdf981995a91</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7069af551bc0776</t>
+          <t>https://www.indeed.com/viewjob?jk=215a62808c4ca701</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Developer - ETL</t>
+          <t>Senior Software Engineer II (Data Pipelines)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ExcelaCom</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Hive, Scala, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8b2e1080230339</t>
+          <t>https://www.indeed.com/viewjob?jk=2c05594fa5c03a89</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks and Cloud</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Azure, Databricks, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ec1ef182d61019</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5c7e1664edb9d4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Azure dotNet AI Integration Developer</t>
+          <t>Senior Software Engineer – Full Stack / Backend / AI Systems</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Berlin Packaging</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Kafka, Oracle</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc29c100a8b89c42</t>
+          <t>https://www.indeed.com/viewjob?jk=2ee3d7ccc5b43286</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Application Engineer II</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Kafka, SQL Server, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5697b129c567549</t>
+          <t>https://www.indeed.com/viewjob?jk=b88bdbb7db1c1b00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Analytics Engineer 2</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e7ead749ef677c7</t>
+          <t>https://www.indeed.com/viewjob?jk=45fd760fc1984df4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ellucian</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1dae4f6c34916d4</t>
+          <t>https://www.indeed.com/viewjob?jk=3742efecc003f285</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azure Cloud Solutions Developer / Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Doeren Mayhew CPAs and Advisors</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, SQL Server, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16b1ba2fceeeff4</t>
+          <t>https://www.indeed.com/viewjob?jk=e7069af551bc0776</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Feature Engineer</t>
+          <t>Activision 2027 Summer Internships - Analytics Engineering</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc268f2e08eed41b</t>
+          <t>https://www.indeed.com/viewjob?jk=a151a475ceda8359</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Data Developer - ETL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>ExcelaCom</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Amherst, NY, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40cbadc2d21dbaf</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8b2e1080230339</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Platform Engineer - Databricks and Cloud</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Azure, Databricks, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f5698c0d5c0c74</t>
+          <t>https://www.indeed.com/viewjob?jk=c7ec1ef182d61019</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Sr. Azure dotNet AI Integration Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Berlin Packaging</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brooklyn, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,102 +1686,102 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59e4133cbdb8ecb</t>
+          <t>https://www.indeed.com/viewjob?jk=dc29c100a8b89c42</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Senior Integration Developer - API Platform</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>TBC Corporation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301dcda44c4f6fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0eebe66ead5b17</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer - Equities Technology</t>
+          <t>Application Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>S3, RDS, Azure, Scala, Kafka, SQL Server, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ef51fce4a7feef</t>
+          <t>https://www.indeed.com/viewjob?jk=b5697b129c567549</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer 2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
+          <t>AWS, EMR, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd06fb948a236148</t>
+          <t>https://www.indeed.com/viewjob?jk=8e7ead749ef677c7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Ellucian</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c059719ff1f4a84</t>
+          <t>https://www.indeed.com/viewjob?jk=a1dae4f6c34916d4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Insights Delivery Merch (Hybrid - Seattle, WA)</t>
+          <t>Azure Cloud Solutions Developer / Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Doeren Mayhew CPAs and Advisors</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, SQL Server, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e052b75c19429d44</t>
+          <t>https://www.indeed.com/viewjob?jk=f16b1ba2fceeeff4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer</t>
+          <t>Senior Feature Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce267e690cfe27d7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc268f2e08eed41b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Contract)</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Colaberry</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Amherst, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afd4daee0cfbd6a</t>
+          <t>https://www.indeed.com/viewjob?jk=c40cbadc2d21dbaf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Contract)</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Colaberry</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb309dc36a3ade0</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f5698c0d5c0c74</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Brooklyn, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700edad9dfcb975f</t>
+          <t>https://www.indeed.com/viewjob?jk=b59e4133cbdb8ecb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff7ed7ce6374b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=301dcda44c4f6fc9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, RDS, BigQuery, Dataflow, Cloud Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions</t>
+          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9545abd3a0f68d</t>
+          <t>https://www.indeed.com/viewjob?jk=dd06fb948a236148</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=348bb65020d238ec</t>
+          <t>https://www.indeed.com/viewjob?jk=3c059719ff1f4a84</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior Data Engineer, Insights Delivery Merch (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cb87de2d0210269</t>
+          <t>https://www.indeed.com/viewjob?jk=e052b75c19429d44</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VRN Technologies</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, Scala, Snowflake</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6a06ecdadb7f76</t>
+          <t>https://www.indeed.com/viewjob?jk=ce267e690cfe27d7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MLOps Engineer II</t>
+          <t>Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Colaberry</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e2aae4eab6d41c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8afd4daee0cfbd6a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Colaberry</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f16755404b284eb</t>
+          <t>https://www.indeed.com/viewjob?jk=feb309dc36a3ade0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198a1d32c3c5a248</t>
+          <t>https://www.indeed.com/viewjob?jk=348bb65020d238ec</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>IAM, RDS, BigQuery, Dataflow, Cloud Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab128e3501b51439</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9545abd3a0f68d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Persistent Systems</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f12f5f159f8687e2</t>
+          <t>https://www.indeed.com/viewjob?jk=eff7ed7ce6374b3b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, GCP, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809926ba4c12a008</t>
+          <t>https://www.indeed.com/viewjob?jk=198a1d32c3c5a248</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Storage Platform Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41755acf2e74e13</t>
+          <t>https://www.indeed.com/viewjob?jk=700edad9dfcb975f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>VRN Technologies</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d4577fc7f8f41d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6a06ecdadb7f76</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60af316cfb20b16</t>
+          <t>https://www.indeed.com/viewjob?jk=4f16755404b284eb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,102 +2526,102 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=345c319d29f5fb24</t>
+          <t>https://www.indeed.com/viewjob?jk=3cb87de2d0210269</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior DevOps engineer.</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ayla Networks</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, Cassandra, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77b42dadc3d64bb</t>
+          <t>https://www.indeed.com/viewjob?jk=ab128e3501b51439</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Persistent Systems</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae52bab9bde8833</t>
+          <t>https://www.indeed.com/viewjob?jk=f12f5f159f8687e2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, GCP, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ef430c583f0949</t>
+          <t>https://www.indeed.com/viewjob?jk=809926ba4c12a008</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Storage Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>S3, RDS, Scala, Snowflake, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ef978918551b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a41755acf2e74e13</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Forward Developed Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637d2d6e8ea9d1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9d1ab5ee809ca2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Cloud Infrastructure &amp; DevOps Engineer</t>
+          <t>MLOps Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ambarella</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d92d093b53bf68d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e2aae4eab6d41c6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Power BI Data Engineer</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564e7d0106f9c065</t>
+          <t>https://www.indeed.com/viewjob?jk=5141a554cf1e2b91</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
+          <t>Senior Software Engineer, CEA - ThousandEyes (Hybrid)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Vantive</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Scala, Kafka, NoSQL, Maven, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b951826f674481d</t>
+          <t>https://www.indeed.com/viewjob?jk=4fba99aaf358701a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, ETL, Git</t>
+          <t>RDS, Hadoop, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c740e2d589eb308c</t>
+          <t>https://www.indeed.com/viewjob?jk=17d4577fc7f8f41d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=822b2e4556cf1c5f</t>
+          <t>https://www.indeed.com/viewjob?jk=e60af316cfb20b16</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba247d1fc82d579c</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae52bab9bde8833</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0849ec21c1c08</t>
+          <t>https://www.indeed.com/viewjob?jk=a56325de82ab5543</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps engineer.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Ayla Networks</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, Cassandra, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56325de82ab5543</t>
+          <t>https://www.indeed.com/viewjob?jk=a77b42dadc3d64bb</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c34fa2d9b2a5c0cf</t>
+          <t>https://www.indeed.com/viewjob?jk=564e7d0106f9c065</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9141d944a31a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=92ef430c583f0949</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d833ee1e80654c8</t>
+          <t>https://www.indeed.com/viewjob?jk=637d2d6e8ea9d1ef</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=280e75cabd3c6a06</t>
+          <t>https://www.indeed.com/viewjob?jk=ba247d1fc82d579c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Junior Full Stack Software Engineer AI and Cloud Applications</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Agility Technologies Inc</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2063590dad13da</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0849ec21c1c08</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Business Analyst - Data Intelligence</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d035d7c47f5688b5</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ef978918551b6c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LexisNexis Reed Tech</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Horsham, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ef43c8ccb7678a</t>
+          <t>https://www.indeed.com/viewjob?jk=345c319d29f5fb24</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Horsham, PA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b853a7d928445871</t>
+          <t>https://www.indeed.com/viewjob?jk=c34fa2d9b2a5c0cf</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Horsham, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bcb4fe5f29db11</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9141d944a31a5a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Solutions Architect – Data Analytics (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Databricks Lakehouse, Power BI, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25bb148408c57615</t>
+          <t>https://www.indeed.com/viewjob?jk=6d833ee1e80654c8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Taxrise</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8be5c844ecb981</t>
+          <t>https://www.indeed.com/viewjob?jk=280e75cabd3c6a06</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Developer Cloud &amp; Distributed Systems</t>
+          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Vantive</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,147 +3391,147 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Cassandra, ETL, CI/CD, Kubernetes</t>
+          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9407487c3afcb12c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b951826f674481d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Hallmark</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d1b36881ddad57</t>
+          <t>https://www.indeed.com/viewjob?jk=c740e2d589eb308c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Youth Villages</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f8c0277359b3cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=822b2e4556cf1c5f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Junior Full Stack Software Engineer AI and Cloud Applications</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Crane Aerospace &amp; Electronics</t>
+          <t>Agility Technologies Inc</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Lynnwood, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Oracle, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df8e9130941aedc7</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2063590dad13da</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr Enterprise Data Platform and Engineering</t>
+          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Academy Sports + Outdoors</t>
+          <t>LexisNexis Reed Tech</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Katy, TX, US USA</t>
+          <t>Horsham, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7fe15b0b60a4d2</t>
+          <t>https://www.indeed.com/viewjob?jk=81ef43c8ccb7678a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Horsham, PA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2654e3bd2509e90</t>
+          <t>https://www.indeed.com/viewjob?jk=b853a7d928445871</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>Solutions Architect – Data Analytics (Remote)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Ferguson</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Databricks Lakehouse, Power BI, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1354b65cdd4f0090</t>
+          <t>https://www.indeed.com/viewjob?jk=25bb148408c57615</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cloud Engineer II- AWS</t>
+          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pittsford, NY, US USA</t>
+          <t>Horsham, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cce58f883c3524b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bcb4fe5f29db11</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Application Security Engineer</t>
+          <t>Business Analyst - Data Intelligence</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>REPAY</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4be196fbc9a16bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d035d7c47f5688b5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Platform Administration Architect</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Wesco</t>
+          <t>Taxrise</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,67 +3716,67 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1276474c632f42</t>
+          <t>https://www.indeed.com/viewjob?jk=4d8be5c844ecb981</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Technology Business Engineer</t>
+          <t>Systems Programmer Analyst l - Java</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ochsner Health</t>
+          <t>Brown Brothers Harriman</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jefferson, LA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Tableau, CI/CD</t>
+          <t>RDS, Kafka, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e95b750693e2318f</t>
+          <t>https://www.indeed.com/viewjob?jk=94250490a5dea702</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>IT Architect 5 TX - Enterprise Data &amp; Analytics - FT - Days</t>
+          <t>Software Developer Cloud &amp; Distributed Systems</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>UC Irvine Health</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Azure, Databricks, GCP, Snowflake, Oracle, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Cassandra, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87e85e74388cdd06</t>
+          <t>https://www.indeed.com/viewjob?jk=9407487c3afcb12c</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>TBC Corporation</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0920adba0ab6199</t>
+          <t>https://www.indeed.com/viewjob?jk=2057a1a27d77eb5f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr Software Engineer Azure &amp; Microsoft Cloud</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Leggett &amp; Platt</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git, Azure Monitor</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bdf03283a9a5d27</t>
+          <t>https://www.indeed.com/viewjob?jk=f2654e3bd2509e90</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>adonis</t>
+          <t>Hallmark</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,17 +3881,437 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI, Git, Python</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19d1b36881ddad57</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Data Engineer - Compensation Systems</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Sunbelt Rentals</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1354b65cdd4f0090</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sr Enterprise Data Platform and Engineering</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Academy Sports + Outdoors</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Katy, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e7fe15b0b60a4d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Crane Aerospace &amp; Electronics</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Lynnwood, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Oracle, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df8e9130941aedc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Cloud Engineer II- AWS</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Pittsford, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform, AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cce58f883c3524b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>IT Architect 5 TX - Enterprise Data &amp; Analytics - FT - Days</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>UC Irvine Health</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Athena, RDS, Azure, Databricks, GCP, Snowflake, Oracle, ETL</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87e85e74388cdd06</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Application Security Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>REPAY</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4be196fbc9a16bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Technology Business Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Ochsner Health</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Jefferson, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e95b750693e2318f</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Data Platform Administration Architect</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Wesco</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d1276474c632f42</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Horizon Media, Inc.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, Docker</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e34e091d0140c14</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer Azure &amp; Microsoft Cloud</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Leggett &amp; Platt</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Lenexa, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bdf03283a9a5d27</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>adonis</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
           <t>AWS, S3, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Git, Bitbucket, Datadog</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d5f405cef6030adc</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Samsara</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0920adba0ab6199</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-11.xlsx
+++ b/results/job_matches_2026-09-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Integration Engineer</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HomeServices of America</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dece858441573583</t>
+          <t>https://www.indeed.com/viewjob?jk=d231c0429c2d5a82</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>Sr Data Integration Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>HomeServices of America</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d231c0429c2d5a82</t>
+          <t>https://www.indeed.com/viewjob?jk=dece858441573583</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>(1112754) Senior Software Engineer - Java/AWS Backend</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Diversified Services Network</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f823b2967bc25ff</t>
+          <t>https://www.indeed.com/viewjob?jk=060cda39e6c67619</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e5ebe6596fd5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=79a2550e31c47b05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>(1112754) Senior Software Engineer - Java/AWS Backend</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Diversified Services Network</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a2550e31c47b05</t>
+          <t>https://www.indeed.com/viewjob?jk=eab311aee9088816</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f454c459d8715c2</t>
+          <t>https://www.indeed.com/viewjob?jk=4f823b2967bc25ff</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>(1112754) Senior Software Engineer - Java/AWS Backend</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Diversified Services Network</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab311aee9088816</t>
+          <t>https://www.indeed.com/viewjob?jk=53e5ebe6596fd5cc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>(1112754) Senior Software Engineer - Java/AWS Backend</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Diversified Services Network</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=060cda39e6c67619</t>
+          <t>https://www.indeed.com/viewjob?jk=9f454c459d8715c2</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GenAI Engineer / Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d705b2d3559bb3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=7440e02579888544</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GenAI Engineer / Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbc2ded1357ab6b</t>
+          <t>https://www.indeed.com/viewjob?jk=d705b2d3559bb3c6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GenAI Engineer / Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7440e02579888544</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fca088326cd72d</t>
         </is>
       </c>
     </row>
@@ -1156,29 +1156,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=386200b3002aff99</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2ed4b81dac13d2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GenAI Engineer / Data Scientist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fca088326cd72d</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbc2ded1357ab6b</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2ed4b81dac13d2</t>
+          <t>https://www.indeed.com/viewjob?jk=386200b3002aff99</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Senior Software Engineer II (Data Pipelines)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Finbott</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Hive, Scala, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a62808c4ca701</t>
+          <t>https://www.indeed.com/viewjob?jk=2c05594fa5c03a89</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II (Data Pipelines)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,59 +1326,59 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Hive, Scala, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c05594fa5c03a89</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5c7e1664edb9d4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5c7e1664edb9d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b88bdbb7db1c1b00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Full Stack / Backend / AI Systems</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,15 +1388,15 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ee3d7ccc5b43286</t>
+          <t>https://www.indeed.com/viewjob?jk=45fd760fc1984df4</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88bdbb7db1c1b00</t>
+          <t>https://www.indeed.com/viewjob?jk=3742efecc003f285</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45fd760fc1984df4</t>
+          <t>https://www.indeed.com/viewjob?jk=e7069af551bc0776</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Activision 2027 Summer Internships - Analytics Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3742efecc003f285</t>
+          <t>https://www.indeed.com/viewjob?jk=a151a475ceda8359</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Data Developer - ETL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ExcelaCom</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7069af551bc0776</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8b2e1080230339</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Activision 2027 Summer Internships - Analytics Engineering</t>
+          <t>Application Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>S3, RDS, Azure, Scala, Kafka, SQL Server, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a151a475ceda8359</t>
+          <t>https://www.indeed.com/viewjob?jk=b5697b129c567549</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Developer - ETL</t>
+          <t>Platform Engineer - Databricks and Cloud</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ExcelaCom</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Azure, Databricks, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8b2e1080230339</t>
+          <t>https://www.indeed.com/viewjob?jk=c7ec1ef182d61019</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks and Cloud</t>
+          <t>Senior Integration Developer - API Platform</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>TBC Corporation</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Azure, Databricks, Scala</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ec1ef182d61019</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0eebe66ead5b17</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Azure dotNet AI Integration Developer</t>
+          <t>Analytics Engineer 2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Berlin Packaging</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Kafka, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc29c100a8b89c42</t>
+          <t>https://www.indeed.com/viewjob?jk=8e7ead749ef677c7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Integration Developer - API Platform</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TBC Corporation</t>
+          <t>Ellucian</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0eebe66ead5b17</t>
+          <t>https://www.indeed.com/viewjob?jk=a1dae4f6c34916d4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Application Engineer II</t>
+          <t>Azure Cloud Solutions Developer / Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Doeren Mayhew CPAs and Advisors</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Kafka, SQL Server, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, SQL Server, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5697b129c567549</t>
+          <t>https://www.indeed.com/viewjob?jk=f16b1ba2fceeeff4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Engineer 2</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Brooklyn, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e7ead749ef677c7</t>
+          <t>https://www.indeed.com/viewjob?jk=b59e4133cbdb8ecb</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ellucian</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Amherst, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1dae4f6c34916d4</t>
+          <t>https://www.indeed.com/viewjob?jk=c40cbadc2d21dbaf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Azure Cloud Solutions Developer / Engineer</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Doeren Mayhew CPAs and Advisors</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, SQL Server, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16b1ba2fceeeff4</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f5698c0d5c0c74</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Feature Engineer</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc268f2e08eed41b</t>
+          <t>https://www.indeed.com/viewjob?jk=301dcda44c4f6fc9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Senior Feature Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Amherst, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40cbadc2d21dbaf</t>
+          <t>https://www.indeed.com/viewjob?jk=fc268f2e08eed41b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f5698c0d5c0c74</t>
+          <t>https://www.indeed.com/viewjob?jk=dd06fb948a236148</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brooklyn, OH, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59e4133cbdb8ecb</t>
+          <t>https://www.indeed.com/viewjob?jk=3c059719ff1f4a84</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Senior Data Engineer, Insights Delivery Merch (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301dcda44c4f6fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=e052b75c19429d44</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd06fb948a236148</t>
+          <t>https://www.indeed.com/viewjob?jk=ce267e690cfe27d7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Colaberry</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c059719ff1f4a84</t>
+          <t>https://www.indeed.com/viewjob?jk=feb309dc36a3ade0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Insights Delivery Merch (Hybrid - Seattle, WA)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
+          <t>IAM, RDS, BigQuery, Dataflow, Cloud Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e052b75c19429d44</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9545abd3a0f68d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce267e690cfe27d7</t>
+          <t>https://www.indeed.com/viewjob?jk=198a1d32c3c5a248</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Colaberry</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afd4daee0cfbd6a</t>
+          <t>https://www.indeed.com/viewjob?jk=eff7ed7ce6374b3b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Contract)</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Colaberry</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb309dc36a3ade0</t>
+          <t>https://www.indeed.com/viewjob?jk=348bb65020d238ec</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=348bb65020d238ec</t>
+          <t>https://www.indeed.com/viewjob?jk=700edad9dfcb975f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, RDS, BigQuery, Dataflow, Cloud Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9545abd3a0f68d</t>
+          <t>https://www.indeed.com/viewjob?jk=3cb87de2d0210269</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Colaberry</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff7ed7ce6374b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=8afd4daee0cfbd6a</t>
         </is>
       </c>
     </row>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>VRN Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198a1d32c3c5a248</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6a06ecdadb7f76</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>MLOps Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700edad9dfcb975f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e2aae4eab6d41c6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VRN Technologies</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6a06ecdadb7f76</t>
+          <t>https://www.indeed.com/viewjob?jk=4f16755404b284eb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Persistent Systems</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f16755404b284eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f12f5f159f8687e2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior Storage Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>S3, RDS, Scala, Snowflake, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cb87de2d0210269</t>
+          <t>https://www.indeed.com/viewjob?jk=a41755acf2e74e13</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,77 +2551,77 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, GCP, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab128e3501b51439</t>
+          <t>https://www.indeed.com/viewjob?jk=809926ba4c12a008</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Persistent Systems</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f12f5f159f8687e2</t>
+          <t>https://www.indeed.com/viewjob?jk=5141a554cf1e2b91</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer, CEA - ThousandEyes (Hybrid)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, GCP, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Scala, Kafka, NoSQL, Maven, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809926ba4c12a008</t>
+          <t>https://www.indeed.com/viewjob?jk=4fba99aaf358701a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Storage Platform Engineer</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Hadoop, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41755acf2e74e13</t>
+          <t>https://www.indeed.com/viewjob?jk=17d4577fc7f8f41d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Forward Developed Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,59 +2701,59 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9d1ab5ee809ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=e60af316cfb20b16</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MLOps Engineer II</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Hive, Spark, PySpark, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e2aae4eab6d41c6</t>
+          <t>https://www.indeed.com/viewjob?jk=56ed3d25e2b81e91</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5141a554cf1e2b91</t>
+          <t>https://www.indeed.com/viewjob?jk=ba247d1fc82d579c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, CEA - ThousandEyes (Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Scala, Kafka, NoSQL, Maven, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fba99aaf358701a</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0849ec21c1c08</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d4577fc7f8f41d</t>
+          <t>https://www.indeed.com/viewjob?jk=a56325de82ab5543</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60af316cfb20b16</t>
+          <t>https://www.indeed.com/viewjob?jk=92ef430c583f0949</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae52bab9bde8833</t>
+          <t>https://www.indeed.com/viewjob?jk=f9ef978918551b6c</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56325de82ab5543</t>
+          <t>https://www.indeed.com/viewjob?jk=345c319d29f5fb24</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior DevOps engineer.</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ayla Networks</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, Cassandra, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77b42dadc3d64bb</t>
+          <t>https://www.indeed.com/viewjob?jk=c34fa2d9b2a5c0cf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Power BI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564e7d0106f9c065</t>
+          <t>https://www.indeed.com/viewjob?jk=637d2d6e8ea9d1ef</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ef430c583f0949</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9141d944a31a5a</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637d2d6e8ea9d1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6d833ee1e80654c8</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba247d1fc82d579c</t>
+          <t>https://www.indeed.com/viewjob?jk=280e75cabd3c6a06</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0849ec21c1c08</t>
+          <t>https://www.indeed.com/viewjob?jk=564e7d0106f9c065</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps engineer.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Ayla Networks</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, Cassandra, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ef978918551b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a77b42dadc3d64bb</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=345c319d29f5fb24</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae52bab9bde8833</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c34fa2d9b2a5c0cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c740e2d589eb308c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9141d944a31a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=822b2e4556cf1c5f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Taxrise</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d833ee1e80654c8</t>
+          <t>https://www.indeed.com/viewjob?jk=4d8be5c844ecb981</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Horsham, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=280e75cabd3c6a06</t>
+          <t>https://www.indeed.com/viewjob?jk=b853a7d928445871</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
+          <t>Business Analyst - Data Intelligence</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Vantive</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b951826f674481d</t>
+          <t>https://www.indeed.com/viewjob?jk=d035d7c47f5688b5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Architect – Data Analytics (Remote)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ferguson</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, ETL, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Databricks Lakehouse, Power BI, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c740e2d589eb308c</t>
+          <t>https://www.indeed.com/viewjob?jk=25bb148408c57615</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Horsham, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=822b2e4556cf1c5f</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bcb4fe5f29db11</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Junior Full Stack Software Engineer AI and Cloud Applications</t>
+          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Agility Technologies Inc</t>
+          <t>LexisNexis Reed Tech</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Horsham, PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2063590dad13da</t>
+          <t>https://www.indeed.com/viewjob?jk=81ef43c8ccb7678a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
+          <t>Junior Full Stack Software Engineer AI and Cloud Applications</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LexisNexis Reed Tech</t>
+          <t>Agility Technologies Inc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Horsham, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ef43c8ccb7678a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2063590dad13da</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Horsham, PA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b853a7d928445871</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d64b090a5428a5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Solutions Architect – Data Analytics (Remote)</t>
+          <t>Systems Programmer Analyst l - Java</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Brown Brothers Harriman</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Databricks Lakehouse, Power BI, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Kafka, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25bb148408c57615</t>
+          <t>https://www.indeed.com/viewjob?jk=94250490a5dea702</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
+          <t>Software Developer Cloud &amp; Distributed Systems</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Horsham, PA, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Cassandra, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bcb4fe5f29db11</t>
+          <t>https://www.indeed.com/viewjob?jk=9407487c3afcb12c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Business Analyst - Data Intelligence</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>TBC Corporation</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d035d7c47f5688b5</t>
+          <t>https://www.indeed.com/viewjob?jk=2057a1a27d77eb5f</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Taxrise</t>
+          <t>Crane Aerospace &amp; Electronics</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Lynnwood, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Oracle, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,67 +3716,67 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8be5c844ecb981</t>
+          <t>https://www.indeed.com/viewjob?jk=df8e9130941aedc7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Systems Programmer Analyst l - Java</t>
+          <t>Cloud Engineer II- AWS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Brown Brothers Harriman</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Pittsford, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94250490a5dea702</t>
+          <t>https://www.indeed.com/viewjob?jk=cce58f883c3524b4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Developer Cloud &amp; Distributed Systems</t>
+          <t>Sr Enterprise Data Platform and Engineering</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Academy Sports + Outdoors</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Katy, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Cassandra, ETL, CI/CD, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9407487c3afcb12c</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7fe15b0b60a4d2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TBC Corporation</t>
+          <t>Hallmark</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,24 +3811,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2057a1a27d77eb5f</t>
+          <t>https://www.indeed.com/viewjob?jk=19d1b36881ddad57</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2654e3bd2509e90</t>
+          <t>https://www.indeed.com/viewjob?jk=1354b65cdd4f0090</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer (remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Hallmark</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d1b36881ddad57</t>
+          <t>https://www.indeed.com/viewjob?jk=f2654e3bd2509e90</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer - Compensation Systems</t>
+          <t>Fullstack Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>Horizon Media, Inc.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1354b65cdd4f0090</t>
+          <t>https://www.indeed.com/viewjob?jk=2e34e091d0140c14</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr Enterprise Data Platform and Engineering</t>
+          <t>IT Architect 5 TX - Enterprise Data &amp; Analytics - FT - Days</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Academy Sports + Outdoors</t>
+          <t>UC Irvine Health</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Katy, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, EMR, Athena, RDS, Azure, Databricks, GCP, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7fe15b0b60a4d2</t>
+          <t>https://www.indeed.com/viewjob?jk=87e85e74388cdd06</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Technology Business Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Crane Aerospace &amp; Electronics</t>
+          <t>Ochsner Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lynnwood, WA, US USA</t>
+          <t>Jefferson, LA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Oracle, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df8e9130941aedc7</t>
+          <t>https://www.indeed.com/viewjob?jk=e95b750693e2318f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cloud Engineer II- AWS</t>
+          <t>Application Security Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>REPAY</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pittsford, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cce58f883c3524b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d4be196fbc9a16bc</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>IT Architect 5 TX - Enterprise Data &amp; Analytics - FT - Days</t>
+          <t>Data Platform Administration Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>UC Irvine Health</t>
+          <t>Wesco</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Azure, Databricks, GCP, Snowflake, Oracle, ETL</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87e85e74388cdd06</t>
+          <t>https://www.indeed.com/viewjob?jk=4d1276474c632f42</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Application Security Engineer</t>
+          <t>Sr Software Engineer Azure &amp; Microsoft Cloud</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>REPAY</t>
+          <t>Leggett &amp; Platt</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git, Azure Monitor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4be196fbc9a16bc</t>
+          <t>https://www.indeed.com/viewjob?jk=7bdf03283a9a5d27</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Technology Business Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ochsner Health</t>
+          <t>adonis</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jefferson, LA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Git, Bitbucket, Datadog</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,182 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e95b750693e2318f</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Data Platform Administration Architect</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Wesco</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1276474c632f42</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Fullstack Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Horizon Media, Inc.</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, Docker</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e34e091d0140c14</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer Azure &amp; Microsoft Cloud</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Leggett &amp; Platt</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Lenexa, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7bdf03283a9a5d27</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>adonis</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Git, Bitbucket, Datadog</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=d5f405cef6030adc</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Samsara</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0920adba0ab6199</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-11.xlsx
+++ b/results/job_matches_2026-09-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Platform &amp; Data Engineer III</t>
+          <t>Consultant, Data Engineer | Snowflake Data Engineer (Python / Snowpark)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b8d6e4d98fa228</t>
+          <t>https://www.indeed.com/viewjob?jk=3affdaaa77646055</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Data Architect – Databricks</t>
+          <t>Platform &amp; Data Engineer III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Google Cloud Platform</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3814c47fcd40bb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=05b8d6e4d98fa228</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>Senior Data Engineer / Data Architect – Databricks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, S3, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d231c0429c2d5a82</t>
+          <t>https://www.indeed.com/viewjob?jk=3814c47fcd40bb0f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Data Integration Engineer</t>
+          <t>GCP Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HomeServices of America</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dece858441573583</t>
+          <t>https://www.indeed.com/viewjob?jk=d231c0429c2d5a82</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>(1112754) Senior Software Engineer - Java/AWS Backend</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Diversified Services Network</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=060cda39e6c67619</t>
+          <t>https://www.indeed.com/viewjob?jk=4f823b2967bc25ff</t>
         </is>
       </c>
     </row>
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Site Reliability Engineer - FedRAMP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Hive, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab311aee9088816</t>
+          <t>https://www.indeed.com/viewjob?jk=b70689612d7d51ee</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>(1112754) Senior Software Engineer - Java/AWS Backend</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diversified Services Network</t>
+          <t>EIS Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f823b2967bc25ff</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6ad6527a71b393</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>(1112754) Senior Software Engineer - Java/AWS Backend</t>
+          <t>Morgan WM Java + Python - C1 - Level</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Diversified Services Network</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,54 +776,54 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e5ebe6596fd5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=2237bdba45156557</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>(1112754) Senior Software Engineer - Java/AWS Backend</t>
+          <t>GenAI Engineer / Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Diversified Services Network</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f454c459d8715c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7440e02579888544</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>(1112164) Senior Software Engineer - Java/AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Diversified Services Network</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e81425a0990a5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=d705b2d3559bb3c6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>(1112164) Senior Software Engineer - Java/AWS</t>
+          <t>AI /ML Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Diversified Services Network</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b1ca06bddd5e551</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2ed4b81dac13d2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - FedRAMP</t>
+          <t>GenAI Engineer / Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Hive, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,102 +916,102 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b70689612d7d51ee</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbc2ded1357ab6b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIS Group</t>
+          <t>Alignment Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6ad6527a71b393</t>
+          <t>https://www.indeed.com/viewjob?jk=27ebfdf981995a91</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Morgan WM Java + Python - C1 - Level</t>
+          <t>Senior Developer W Cloud-Native Data AWS Kafka</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Volantsoft Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2237bdba45156557</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd24f1dcad4258c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer II (Data Pipelines)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Hive, Scala, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5f05e5a352797a</t>
+          <t>https://www.indeed.com/viewjob?jk=2c05594fa5c03a89</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GenAI Engineer / Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,102 +1056,102 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7440e02579888544</t>
+          <t>https://www.indeed.com/viewjob?jk=6eab47ece7c9f23b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d705b2d3559bb3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8fccc8f57dde6104</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Visualization Developer/Full Stack Developer - Contractor</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Dragonfly Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fca088326cd72d</t>
+          <t>https://www.indeed.com/viewjob?jk=261266691bb3209c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI /ML Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2ed4b81dac13d2</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5c7e1664edb9d4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GenAI Engineer / Data Scientist</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbc2ded1357ab6b</t>
+          <t>https://www.indeed.com/viewjob?jk=b88bdbb7db1c1b00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI /ML Data Scientist</t>
+          <t>Data Developer - ETL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ExcelaCom</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=386200b3002aff99</t>
+          <t>https://www.indeed.com/viewjob?jk=5f8b2e1080230339</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Application Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alignment Health</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>S3, RDS, Azure, Scala, Kafka, SQL Server, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27ebfdf981995a91</t>
+          <t>https://www.indeed.com/viewjob?jk=b5697b129c567549</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II (Data Pipelines)</t>
+          <t>Sr. Azure dotNet AI Integration Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Berlin Packaging</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Hive, Scala, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c05594fa5c03a89</t>
+          <t>https://www.indeed.com/viewjob?jk=dc29c100a8b89c42</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Platform Engineer - Databricks and Cloud</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Azure, Databricks, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5c7e1664edb9d4</t>
+          <t>https://www.indeed.com/viewjob?jk=c7ec1ef182d61019</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Integration Developer - API Platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TBC Corporation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88bdbb7db1c1b00</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0eebe66ead5b17</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Activision 2027 Summer Internships - Analytics Engineering</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45fd760fc1984df4</t>
+          <t>https://www.indeed.com/viewjob?jk=a151a475ceda8359</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Analytics Engineer 2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
+          <t>AWS, EMR, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3742efecc003f285</t>
+          <t>https://www.indeed.com/viewjob?jk=8e7ead749ef677c7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ellucian</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7069af551bc0776</t>
+          <t>https://www.indeed.com/viewjob?jk=a1dae4f6c34916d4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Activision 2027 Summer Internships - Analytics Engineering</t>
+          <t>Senior Feature Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a151a475ceda8359</t>
+          <t>https://www.indeed.com/viewjob?jk=fc268f2e08eed41b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Developer - ETL</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ExcelaCom</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
+          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8b2e1080230339</t>
+          <t>https://www.indeed.com/viewjob?jk=dd06fb948a236148</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Application Engineer II</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Kafka, SQL Server, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5697b129c567549</t>
+          <t>https://www.indeed.com/viewjob?jk=ce267e690cfe27d7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks and Cloud</t>
+          <t>Senior Data Engineer, Insights Delivery Merch (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Azure, Databricks, Scala</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ec1ef182d61019</t>
+          <t>https://www.indeed.com/viewjob?jk=e052b75c19429d44</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Integration Developer - API Platform</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TBC Corporation</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0eebe66ead5b17</t>
+          <t>https://www.indeed.com/viewjob?jk=700edad9dfcb975f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Analytics Engineer 2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e7ead749ef677c7</t>
+          <t>https://www.indeed.com/viewjob?jk=eff7ed7ce6374b3b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ellucian</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, BigQuery, Dataflow, Cloud Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,102 +1721,102 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1dae4f6c34916d4</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9545abd3a0f68d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Azure Cloud Solutions Developer / Engineer</t>
+          <t>Senior Java Developer (Spring Boot &amp; AWS Glue)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Doeren Mayhew CPAs and Advisors</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, SQL Server, Power BI, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16b1ba2fceeeff4</t>
+          <t>https://www.indeed.com/viewjob?jk=19c62182c1dfd5a0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Senior Software Engineer - AI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brooklyn, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59e4133cbdb8ecb</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a45a47cc178b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Amherst, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40cbadc2d21dbaf</t>
+          <t>https://www.indeed.com/viewjob?jk=4f16755404b284eb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, Talend, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f5698c0d5c0c74</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb5a16405efb7b8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>MLOps Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301dcda44c4f6fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e2aae4eab6d41c6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Feature Engineer</t>
+          <t>Senior Storage Platform Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>S3, RDS, Scala, Snowflake, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc268f2e08eed41b</t>
+          <t>https://www.indeed.com/viewjob?jk=a41755acf2e74e13</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, GCP, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd06fb948a236148</t>
+          <t>https://www.indeed.com/viewjob?jk=809926ba4c12a008</t>
         </is>
       </c>
     </row>
@@ -2008,25 +2008,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Insights Delivery Merch (Hybrid - Seattle, WA)</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
+          <t>RDS, Hadoop, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e052b75c19429d44</t>
+          <t>https://www.indeed.com/viewjob?jk=17d4577fc7f8f41d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer</t>
+          <t>Senior Software Engineer, CEA - ThousandEyes (Hybrid)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Scala, Kafka, NoSQL, Maven, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce267e690cfe27d7</t>
+          <t>https://www.indeed.com/viewjob?jk=4fba99aaf358701a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Contract)</t>
+          <t>Sr. Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Colaberry</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Spark, PySpark, Scala, NoSQL, MLflow, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,42 +2106,42 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb309dc36a3ade0</t>
+          <t>https://www.indeed.com/viewjob?jk=451b6e29bdbd8304</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, RDS, BigQuery, Dataflow, Cloud Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Hive, Spark, PySpark, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9545abd3a0f68d</t>
+          <t>https://www.indeed.com/viewjob?jk=56ed3d25e2b81e91</t>
         </is>
       </c>
     </row>
@@ -2153,20 +2153,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198a1d32c3c5a248</t>
+          <t>https://www.indeed.com/viewjob?jk=92ef430c583f0949</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps engineer.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ayla Networks</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, Cassandra, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff7ed7ce6374b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=a77b42dadc3d64bb</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=348bb65020d238ec</t>
+          <t>https://www.indeed.com/viewjob?jk=564e7d0106f9c065</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,102 +2281,102 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700edad9dfcb975f</t>
+          <t>https://www.indeed.com/viewjob?jk=637d2d6e8ea9d1ef</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cb87de2d0210269</t>
+          <t>https://www.indeed.com/viewjob?jk=c740e2d589eb308c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Colaberry</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afd4daee0cfbd6a</t>
+          <t>https://www.indeed.com/viewjob?jk=822b2e4556cf1c5f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VRN Technologies</t>
+          <t>Taxrise</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, Scala, Snowflake</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6a06ecdadb7f76</t>
+          <t>https://www.indeed.com/viewjob?jk=4d8be5c844ecb981</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MLOps Engineer II</t>
+          <t>Junior Full Stack Software Engineer AI and Cloud Applications</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Agility Technologies Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e2aae4eab6d41c6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2063590dad13da</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Solutions Architect – Data Analytics (Remote)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Ferguson</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Databricks Lakehouse, Power BI, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f16755404b284eb</t>
+          <t>https://www.indeed.com/viewjob?jk=25bb148408c57615</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Persistent Systems</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f12f5f159f8687e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d64b090a5428a5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Storage Platform Engineer</t>
+          <t>Business Analyst - Data Intelligence</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41755acf2e74e13</t>
+          <t>https://www.indeed.com/viewjob?jk=d035d7c47f5688b5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>LexisNexis Reed Tech</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Horsham, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, GCP, Vertex AI, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809926ba4c12a008</t>
+          <t>https://www.indeed.com/viewjob?jk=81ef43c8ccb7678a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Horsham, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5141a554cf1e2b91</t>
+          <t>https://www.indeed.com/viewjob?jk=b853a7d928445871</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, CEA - ThousandEyes (Hybrid)</t>
+          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Horsham, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Scala, Kafka, NoSQL, Maven, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fba99aaf358701a</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bcb4fe5f29db11</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d4577fc7f8f41d</t>
+          <t>https://www.indeed.com/viewjob?jk=5141a554cf1e2b91</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Systems Programmer Analyst l - Java</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Brown Brothers Harriman</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>RDS, Kafka, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60af316cfb20b16</t>
+          <t>https://www.indeed.com/viewjob?jk=94250490a5dea702</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Developer Cloud &amp; Distributed Systems</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Hive, Spark, PySpark, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Cassandra, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ed3d25e2b81e91</t>
+          <t>https://www.indeed.com/viewjob?jk=9407487c3afcb12c</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba247d1fc82d579c</t>
+          <t>https://www.indeed.com/viewjob?jk=a56325de82ab5543</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>TBC Corporation</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0849ec21c1c08</t>
+          <t>https://www.indeed.com/viewjob?jk=2057a1a27d77eb5f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Enterprise Data Platform and Engineering</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Academy Sports + Outdoors</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Katy, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56325de82ab5543</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7fe15b0b60a4d2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Crane Aerospace &amp; Electronics</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Lynnwood, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Oracle, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ef430c583f0949</t>
+          <t>https://www.indeed.com/viewjob?jk=df8e9130941aedc7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer II- AWS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsford, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, RDS, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,19 +2911,19 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ef978918551b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=cce58f883c3524b4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cybersecurity Software Engineer II | ML &amp; AI (Remote)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2932,81 +2932,81 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=345c319d29f5fb24</t>
+          <t>https://www.indeed.com/viewjob?jk=7243ca669e449c88</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>P3+Uplift</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, MySQL, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c34fa2d9b2a5c0cf</t>
+          <t>https://www.indeed.com/viewjob?jk=58d1e81b36b332b5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer Azure &amp; Microsoft Cloud</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Leggett &amp; Platt</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git, Azure Monitor</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637d2d6e8ea9d1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=7bdf03283a9a5d27</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Architect 5 TX - Enterprise Data &amp; Analytics - FT - Days</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>UC Irvine Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, EMR, Athena, RDS, Azure, Databricks, GCP, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9141d944a31a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=87e85e74388cdd06</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technology Business Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Ochsner Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jefferson, LA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d833ee1e80654c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e95b750693e2318f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Administration Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Wesco</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=280e75cabd3c6a06</t>
+          <t>https://www.indeed.com/viewjob?jk=4d1276474c632f42</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Power BI Data Engineer</t>
+          <t>Application Security Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>REPAY</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ELT, dbt</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564e7d0106f9c065</t>
+          <t>https://www.indeed.com/viewjob?jk=d4be196fbc9a16bc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior DevOps engineer.</t>
+          <t>Fullstack Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ayla Networks</t>
+          <t>Horizon Media, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, Cassandra, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77b42dadc3d64bb</t>
+          <t>https://www.indeed.com/viewjob?jk=2e34e091d0140c14</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sunbelt Rentals</t>
+          <t>adonis</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Git, Bitbucket, Datadog</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3225,916 +3225,6 @@
         </is>
       </c>
       <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae52bab9bde8833</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, ETL, Git</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c740e2d589eb308c</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>RS21: A Data Science and Visualization Company</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=822b2e4556cf1c5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior, Data Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Taxrise</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8be5c844ecb981</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>LexisNexis Legal &amp; Professional</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Horsham, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b853a7d928445871</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Business Analyst - Data Intelligence</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>FFF Enterprises</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Flower Mound, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d035d7c47f5688b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Solutions Architect – Data Analytics (Remote)</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Ferguson</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Databricks Lakehouse, Power BI, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=25bb148408c57615</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>RELX Group</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Horsham, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bcb4fe5f29db11</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>LexisNexis Reed Tech</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Horsham, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81ef43c8ccb7678a</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Junior Full Stack Software Engineer AI and Cloud Applications</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Agility Technologies Inc</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2063590dad13da</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Full-Stack AI Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Micron Technology</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d64b090a5428a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Systems Programmer Analyst l - Java</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Brown Brothers Harriman</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Kafka, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94250490a5dea702</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Software Developer Cloud &amp; Distributed Systems</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>San Juan, PR, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Cassandra, ETL, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9407487c3afcb12c</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Cloud Data Architect</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>TBC Corporation</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2057a1a27d77eb5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Crane Aerospace &amp; Electronics</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Lynnwood, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Oracle, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df8e9130941aedc7</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Cloud Engineer II- AWS</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Pittsford, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform, AWS CloudFormation</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cce58f883c3524b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Sr Enterprise Data Platform and Engineering</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Academy Sports + Outdoors</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Katy, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7fe15b0b60a4d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Data Engineer (remote)</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Hallmark</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI, Git, Python</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19d1b36881ddad57</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Data Engineer - Compensation Systems</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Sunbelt Rentals</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Fort Mill, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1354b65cdd4f0090</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Sunbelt Rentals</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Fort Mill, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2654e3bd2509e90</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Fullstack Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Horizon Media, Inc.</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, Docker</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e34e091d0140c14</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>IT Architect 5 TX - Enterprise Data &amp; Analytics - FT - Days</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>UC Irvine Health</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Athena, RDS, Azure, Databricks, GCP, Snowflake, Oracle, ETL</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87e85e74388cdd06</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Technology Business Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Ochsner Health</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Jefferson, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e95b750693e2318f</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Application Security Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>REPAY</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4be196fbc9a16bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Data Platform Administration Architect</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Wesco</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1276474c632f42</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer Azure &amp; Microsoft Cloud</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Leggett &amp; Platt</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Lenexa, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7bdf03283a9a5d27</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>adonis</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Git, Bitbucket, Datadog</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d5f405cef6030adc</t>
         </is>

--- a/results/job_matches_2026-09-11.xlsx
+++ b/results/job_matches_2026-09-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>(1112754) Senior Software Engineer - Java/AWS Backend</t>
+          <t>Devops &amp; Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Diversified Services Network</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f823b2967bc25ff</t>
+          <t>https://www.indeed.com/viewjob?jk=6118bce35a89fad6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>(1112754) Senior Software Engineer - Java/AWS Backend</t>
+          <t>Senior Site Reliability Engineer - FedRAMP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Diversified Services Network</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Hive, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a2550e31c47b05</t>
+          <t>https://www.indeed.com/viewjob?jk=b70689612d7d51ee</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - FedRAMP</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>POOLCORP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Covington, LA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Hive, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b70689612d7d51ee</t>
+          <t>https://www.indeed.com/viewjob?jk=f983e68988cd84c3</t>
         </is>
       </c>
     </row>
@@ -748,35 +748,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Morgan WM Java + Python - C1 - Level</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>United Network For Organ Sharing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2237bdba45156557</t>
+          <t>https://www.indeed.com/viewjob?jk=30ba8d94be3258be</t>
         </is>
       </c>
     </row>
@@ -888,25 +888,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GenAI Engineer / Data Scientist</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Alignment Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbc2ded1357ab6b</t>
+          <t>https://www.indeed.com/viewjob?jk=27ebfdf981995a91</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Developer W Cloud-Native Data AWS Kafka</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alignment Health</t>
+          <t>Volantsoft Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27ebfdf981995a91</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd24f1dcad4258c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Developer W Cloud-Native Data AWS Kafka</t>
+          <t>Senior Software Engineer II (Data Pipelines)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Volantsoft Inc</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Hive, Scala, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd24f1dcad4258c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c05594fa5c03a89</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II (Data Pipelines)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Hive, Scala, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c05594fa5c03a89</t>
+          <t>https://www.indeed.com/viewjob?jk=01a4f8f7abda227f</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88bdbb7db1c1b00</t>
+          <t>https://www.indeed.com/viewjob?jk=f9b9eb4f148a3c61</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Application Engineer II</t>
+          <t>Senior Data Engineer, HR Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>FTI Consulting, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Kafka, SQL Server, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5697b129c567549</t>
+          <t>https://www.indeed.com/viewjob?jk=12df59b44e06ccc3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Azure dotNet AI Integration Developer</t>
+          <t>Activision 2027 Summer Internships - Analytics Engineering</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Berlin Packaging</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Kafka, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc29c100a8b89c42</t>
+          <t>https://www.indeed.com/viewjob?jk=a151a475ceda8359</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks and Cloud</t>
+          <t>Application Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Azure, Databricks, Scala</t>
+          <t>S3, RDS, Azure, Scala, Kafka, SQL Server, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ec1ef182d61019</t>
+          <t>https://www.indeed.com/viewjob?jk=b5697b129c567549</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Integration Developer - API Platform</t>
+          <t>Sr. Azure dotNet AI Integration Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TBC Corporation</t>
+          <t>Berlin Packaging</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0eebe66ead5b17</t>
+          <t>https://www.indeed.com/viewjob?jk=dc29c100a8b89c42</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Activision 2027 Summer Internships - Analytics Engineering</t>
+          <t>Platform Engineer - Databricks and Cloud</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,69 +1396,69 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Azure, Databricks, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a151a475ceda8359</t>
+          <t>https://www.indeed.com/viewjob?jk=c7ec1ef182d61019</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Analytics Engineer 2</t>
+          <t>Senior Integration Developer - API Platform</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>TBC Corporation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ELT, dbt</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e7ead749ef677c7</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0eebe66ead5b17</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Cloud Data Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ellucian</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1dae4f6c34916d4</t>
+          <t>https://www.indeed.com/viewjob?jk=5b433264160b2860</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Feature Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Ellucian</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,129 +1511,129 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc268f2e08eed41b</t>
+          <t>https://www.indeed.com/viewjob?jk=a1dae4f6c34916d4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd06fb948a236148</t>
+          <t>https://www.indeed.com/viewjob?jk=d7f86c244da3f8b1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer</t>
+          <t>Cloud Data Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce267e690cfe27d7</t>
+          <t>https://www.indeed.com/viewjob?jk=08ef3c2039b0fb0d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Insights Delivery Merch (Hybrid - Seattle, WA)</t>
+          <t>Cloud Data Analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e052b75c19429d44</t>
+          <t>https://www.indeed.com/viewjob?jk=26633e481defb97b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Sr. Software Engineer, Firehouse Subs</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Firehouse Subs</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700edad9dfcb975f</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ab4fc88b550f20</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Airflow</t>
+          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff7ed7ce6374b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=dd06fb948a236148</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer, Insights Delivery Merch (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, BigQuery, Dataflow, Cloud Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9545abd3a0f68d</t>
+          <t>https://www.indeed.com/viewjob?jk=e052b75c19429d44</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Java Developer (Spring Boot &amp; AWS Glue)</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c62182c1dfd5a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ce267e690cfe27d7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a45a47cc178b</t>
+          <t>https://www.indeed.com/viewjob?jk=3c059719ff1f4a84</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>IAM, RDS, BigQuery, Dataflow, Cloud Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f16755404b284eb</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9545abd3a0f68d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>Software Engineer II - Data Management</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, Talend, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb5a16405efb7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=fc81d47e989893b9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MLOps Engineer II</t>
+          <t>Data Analytics Engineer / Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Infopro Digital</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e2aae4eab6d41c6</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcc669cec25936b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Storage Platform Engineer</t>
+          <t>Senior Java Developer (Spring Boot &amp; AWS Glue)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Snowflake, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41755acf2e74e13</t>
+          <t>https://www.indeed.com/viewjob?jk=19c62182c1dfd5a0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, GCP, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, Talend, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809926ba4c12a008</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb5a16405efb7b8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - AI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,42 +1991,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c059719ff1f4a84</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a45a47cc178b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>MLOps Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d4577fc7f8f41d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e2aae4eab6d41c6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, CEA - ThousandEyes (Hybrid)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Scala, Kafka, NoSQL, Maven, Docker</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, GCP, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fba99aaf358701a</t>
+          <t>https://www.indeed.com/viewjob?jk=809926ba4c12a008</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, NoSQL, MLflow, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>RDS, Hadoop, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=451b6e29bdbd8304</t>
+          <t>https://www.indeed.com/viewjob?jk=17d4577fc7f8f41d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Hive, Spark, PySpark, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ed3d25e2b81e91</t>
+          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ef430c583f0949</t>
+          <t>https://www.indeed.com/viewjob?jk=88ae16d95ba76f7b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior DevOps engineer.</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ayla Networks</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, Cassandra, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Hive, Spark, PySpark, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77b42dadc3d64bb</t>
+          <t>https://www.indeed.com/viewjob?jk=56ed3d25e2b81e91</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Power BI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564e7d0106f9c065</t>
+          <t>https://www.indeed.com/viewjob?jk=92ef430c583f0949</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637d2d6e8ea9d1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=822b2e4556cf1c5f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer AI Native Delivery</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Taazaa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Hudson, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, ETL, Git</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c740e2d589eb308c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0e3e98bb626a4a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=822b2e4556cf1c5f</t>
+          <t>https://www.indeed.com/viewjob?jk=a56325de82ab5543</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Junior Full Stack Software Engineer AI and Cloud Applications</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Taxrise</t>
+          <t>Agility Technologies Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8be5c844ecb981</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2063590dad13da</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Junior Full Stack Software Engineer AI and Cloud Applications</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Agility Technologies Inc</t>
+          <t>Mirantis</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2063590dad13da</t>
+          <t>https://www.indeed.com/viewjob?jk=ca39720d41d00c5c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Solutions Architect – Data Analytics (Remote)</t>
+          <t>Senior Software Engineer 2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Stellar Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Databricks Lakehouse, Power BI, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25bb148408c57615</t>
+          <t>https://www.indeed.com/viewjob?jk=094c3e48e41b0fa1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Solutions Architect – Data Analytics (Remote)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Ferguson</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Databricks Lakehouse, Power BI, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d64b090a5428a5</t>
+          <t>https://www.indeed.com/viewjob?jk=25bb148408c57615</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Business Analyst - Data Intelligence</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d035d7c47f5688b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5141a554cf1e2b91</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LexisNexis Reed Tech</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Horsham, PA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ef43c8ccb7678a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d64b090a5428a5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
+          <t>Business Analyst - Data Intelligence</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Horsham, PA, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b853a7d928445871</t>
+          <t>https://www.indeed.com/viewjob?jk=d035d7c47f5688b5</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>LexisNexis Reed Tech</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bcb4fe5f29db11</t>
+          <t>https://www.indeed.com/viewjob?jk=81ef43c8ccb7678a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5141a554cf1e2b91</t>
+          <t>https://www.indeed.com/viewjob?jk=637d2d6e8ea9d1ef</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Systems Programmer Analyst l - Java</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Brown Brothers Harriman</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94250490a5dea702</t>
+          <t>https://www.indeed.com/viewjob?jk=345c319d29f5fb24</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Developer Cloud &amp; Distributed Systems</t>
+          <t>Systems Programmer Analyst l - Java</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Brown Brothers Harriman</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Cassandra, ETL, CI/CD, Kubernetes</t>
+          <t>RDS, Kafka, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9407487c3afcb12c</t>
+          <t>https://www.indeed.com/viewjob?jk=94250490a5dea702</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer Cloud &amp; Distributed Systems</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Cassandra, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56325de82ab5543</t>
+          <t>https://www.indeed.com/viewjob?jk=9407487c3afcb12c</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Enterprise Data Platform and Engineering</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Academy Sports + Outdoors</t>
+          <t>Crane Aerospace &amp; Electronics</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Katy, TX, US USA</t>
+          <t>Lynnwood, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Oracle, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7fe15b0b60a4d2</t>
+          <t>https://www.indeed.com/viewjob?jk=df8e9130941aedc7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Engineer II- AWS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Crane Aerospace &amp; Electronics</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lynnwood, WA, US USA</t>
+          <t>Pittsford, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Oracle, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, RDS, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df8e9130941aedc7</t>
+          <t>https://www.indeed.com/viewjob?jk=cce58f883c3524b4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Engineer II- AWS</t>
+          <t>Senior Dynamics 365 - Power Platform Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>AHU Technologies</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pittsford, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cce58f883c3524b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a44cb65cdf117f8c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cybersecurity Software Engineer II | ML &amp; AI (Remote)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>P3+Uplift</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, MySQL, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7243ca669e449c88</t>
+          <t>https://www.indeed.com/viewjob?jk=58d1e81b36b332b5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>CFSA Senior Developer D365 Power Platform Azure</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>P3+Uplift</t>
+          <t>Collaboredge</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, MySQL, Data Modeling, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58d1e81b36b332b5</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56b6f1122d847a</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>IT Architect 5 TX - Enterprise Data &amp; Analytics - FT - Days</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>UC Irvine Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Azure, Databricks, GCP, Snowflake, Oracle, ETL</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87e85e74388cdd06</t>
+          <t>https://www.indeed.com/viewjob?jk=75d4584624626366</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Technology Business Engineer</t>
+          <t>IT Architect 5 TX - Enterprise Data &amp; Analytics - FT - Days</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ochsner Health</t>
+          <t>UC Irvine Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jefferson, LA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, EMR, Athena, RDS, Azure, Databricks, GCP, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e95b750693e2318f</t>
+          <t>https://www.indeed.com/viewjob?jk=87e85e74388cdd06</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Platform Administration Architect</t>
+          <t>Technology Business Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Wesco</t>
+          <t>Ochsner Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jefferson, LA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1276474c632f42</t>
+          <t>https://www.indeed.com/viewjob?jk=e95b750693e2318f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Application Security Engineer</t>
+          <t>Data Platform Administration Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>REPAY</t>
+          <t>Wesco</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4be196fbc9a16bc</t>
+          <t>https://www.indeed.com/viewjob?jk=4d1276474c632f42</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Fullstack Engineer</t>
+          <t>Application Security Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Horizon Media, Inc.</t>
+          <t>REPAY</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, Docker</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,19 +3191,19 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e34e091d0140c14</t>
+          <t>https://www.indeed.com/viewjob?jk=d4be196fbc9a16bc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Fullstack Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>adonis</t>
+          <t>Horizon Media, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, PostgreSQL, CI/CD, Git, Bitbucket, Datadog</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,42 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f405cef6030adc</t>
+          <t>https://www.indeed.com/viewjob?jk=2e34e091d0140c14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Cybersecurity Software Engineer II | ML &amp; AI (Remote)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7243ca669e449c88</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-11.xlsx
+++ b/results/job_matches_2026-09-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,122 +538,122 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Data Architect – Databricks</t>
+          <t>Devops &amp; Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Google Cloud Platform</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3814c47fcd40bb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=6118bce35a89fad6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GCP Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>POOLCORP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Covington, LA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d231c0429c2d5a82</t>
+          <t>https://www.indeed.com/viewjob?jk=f983e68988cd84c3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Devops &amp; Data Pipeline Engineer</t>
+          <t>Senior Site Reliability Engineer - FedRAMP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, Hive, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6118bce35a89fad6</t>
+          <t>https://www.indeed.com/viewjob?jk=b70689612d7d51ee</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - FedRAMP</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>EIS Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Hive, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b70689612d7d51ee</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6ad6527a71b393</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>POOLCORP</t>
+          <t>United Network For Organ Sharing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Covington, LA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f983e68988cd84c3</t>
+          <t>https://www.indeed.com/viewjob?jk=30ba8d94be3258be</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>GenAI Engineer / Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EIS Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,49 +741,49 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6ad6527a71b393</t>
+          <t>https://www.indeed.com/viewjob?jk=7440e02579888544</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>United Network For Organ Sharing</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ba8d94be3258be</t>
+          <t>https://www.indeed.com/viewjob?jk=d705b2d3559bb3c6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GenAI Engineer / Data Scientist</t>
+          <t>AI /ML Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7440e02579888544</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2ed4b81dac13d2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d705b2d3559bb3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2ac2b347d252fa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI /ML Data Scientist</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2ed4b81dac13d2</t>
+          <t>https://www.indeed.com/viewjob?jk=99abac312f847817</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alignment Health</t>
+          <t>Orrstown Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Towson, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, Redshift, S3, Azure, BigQuery, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27ebfdf981995a91</t>
+          <t>https://www.indeed.com/viewjob?jk=566b830bfaf60ca5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Developer W Cloud-Native Data AWS Kafka</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Volantsoft Inc</t>
+          <t>Alignment Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd24f1dcad4258c</t>
+          <t>https://www.indeed.com/viewjob?jk=27ebfdf981995a91</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Java Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
+          <t>AWS, Scala, Kafka, Snowflake, Oracle, DynamoDB, Data Modeling, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01a4f8f7abda227f</t>
+          <t>https://www.indeed.com/viewjob?jk=0ba63ea9a881f407</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Developer W Cloud-Native Data AWS Kafka</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Volantsoft Inc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eab47ece7c9f23b</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd24f1dcad4258c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fccc8f57dde6104</t>
+          <t>https://www.indeed.com/viewjob?jk=67a5f6f5036e1fb8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Developer/Full Stack Developer - Contractor</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dragonfly Health</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=261266691bb3209c</t>
+          <t>https://www.indeed.com/viewjob?jk=01a4f8f7abda227f</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Data Modeling, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5c7e1664edb9d4</t>
+          <t>https://www.indeed.com/viewjob?jk=6eab47ece7c9f23b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9b9eb4f148a3c61</t>
+          <t>https://www.indeed.com/viewjob?jk=8fccc8f57dde6104</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Developer - ETL</t>
+          <t>Senior Data Visualization Developer/Full Stack Developer - Contractor</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ExcelaCom</t>
+          <t>Dragonfly Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, RDS, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f8b2e1080230339</t>
+          <t>https://www.indeed.com/viewjob?jk=261266691bb3209c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, HR Data &amp; Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FTI Consulting, Inc.</t>
+          <t>Hiring Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12df59b44e06ccc3</t>
+          <t>https://www.indeed.com/viewjob?jk=7304c878aae4c5cd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Activision 2027 Summer Internships - Analytics Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a151a475ceda8359</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5c7e1664edb9d4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Application Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Kafka, SQL Server, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5697b129c567549</t>
+          <t>https://www.indeed.com/viewjob?jk=f9b9eb4f148a3c61</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Azure dotNet AI Integration Developer</t>
+          <t>Senior Data Engineer, HR Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Berlin Packaging</t>
+          <t>FTI Consulting, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, Kafka, Oracle</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc29c100a8b89c42</t>
+          <t>https://www.indeed.com/viewjob?jk=12df59b44e06ccc3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Engineer - Databricks and Cloud</t>
+          <t>Activision 2027 Summer Internships - Analytics Engineering</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Azure, Databricks, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ec1ef182d61019</t>
+          <t>https://www.indeed.com/viewjob?jk=a151a475ceda8359</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Integration Developer - API Platform</t>
+          <t>Platform Engineer - Databricks and Cloud</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TBC Corporation</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,69 +1431,69 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, IAM, RDS, Azure, Databricks, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0eebe66ead5b17</t>
+          <t>https://www.indeed.com/viewjob?jk=c7ec1ef182d61019</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Data Analyst</t>
+          <t>Senior Integration Developer - API Platform</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>TBC Corporation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b433264160b2860</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0eebe66ead5b17</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior Software Engineer, Data - SF</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ellucian</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1dae4f6c34916d4</t>
+          <t>https://www.indeed.com/viewjob?jk=eff53b3e177c1286</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7f86c244da3f8b1</t>
+          <t>https://www.indeed.com/viewjob?jk=26633e481defb97b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Data Analyst</t>
+          <t>Senior Software Engineer, Data - SF</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ef3c2039b0fb0d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac4c66a7703e5791</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26633e481defb97b</t>
+          <t>https://www.indeed.com/viewjob?jk=d7f86c244da3f8b1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Firehouse Subs</t>
+          <t>Cloud Data Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Firehouse Subs</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ab4fc88b550f20</t>
+          <t>https://www.indeed.com/viewjob?jk=5b433264160b2860</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd06fb948a236148</t>
+          <t>https://www.indeed.com/viewjob?jk=08ef3c2039b0fb0d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Insights Delivery Merch (Hybrid - Seattle, WA)</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Ellucian</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e052b75c19429d44</t>
+          <t>https://www.indeed.com/viewjob?jk=a1dae4f6c34916d4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Intermediate Software Engineer</t>
+          <t>Software Engineer II - Data Management</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce267e690cfe27d7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc81d47e989893b9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analytics Engineer / Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Infopro Digital</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c059719ff1f4a84</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcc669cec25936b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer, Insights Delivery Merch (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IAM, RDS, BigQuery, Dataflow, Cloud Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9545abd3a0f68d</t>
+          <t>https://www.indeed.com/viewjob?jk=e052b75c19429d44</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer II - Data Management</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, DynamoDB, Data Modeling</t>
+          <t>Redshift, RDS, Databricks, Medallion Architecture, Hadoop, Scala, Snowflake, NoSQL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc81d47e989893b9</t>
+          <t>https://www.indeed.com/viewjob?jk=dd06fb948a236148</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer / Architect</t>
+          <t>Sr. Software Engineer, Firehouse Subs</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Infopro Digital</t>
+          <t>Firehouse Subs</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, dbt, Power BI</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcc669cec25936b</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ab4fc88b550f20</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Java Developer (Spring Boot &amp; AWS Glue)</t>
+          <t>Intermediate Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, Data Modeling, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c62182c1dfd5a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ce267e690cfe27d7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, Talend, CI/CD, Jenkins</t>
+          <t>IAM, RDS, BigQuery, Dataflow, Cloud Storage, Scala, Power BI, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb5a16405efb7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9545abd3a0f68d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI</t>
+          <t>Senior Java Developer (Spring Boot &amp; AWS Glue)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc6a45a47cc178b</t>
+          <t>https://www.indeed.com/viewjob?jk=19c62182c1dfd5a0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MLOps Engineer II</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, Talend, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e2aae4eab6d41c6</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb5a16405efb7b8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer - AI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,77 +2061,77 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, GCP, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809926ba4c12a008</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc6a45a47cc178b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d4577fc7f8f41d</t>
+          <t>https://www.indeed.com/viewjob?jk=213eeef2d3afc755</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Unity Catalog, Scala, ELT, Splunk, DataOps, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a32584106a1cad30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Enterprise Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Hive, Spark, PySpark, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ae16d95ba76f7b</t>
+          <t>https://www.indeed.com/viewjob?jk=56ed3d25e2b81e91</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Hive, Spark, PySpark, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ed3d25e2b81e91</t>
+          <t>https://www.indeed.com/viewjob?jk=88ae16d95ba76f7b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ef430c583f0949</t>
+          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=822b2e4556cf1c5f</t>
+          <t>https://www.indeed.com/viewjob?jk=f87429c065242fc3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Engineer AI Native Delivery</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Taazaa</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hudson, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0e3e98bb626a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=822b2e4556cf1c5f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Hadoop, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56325de82ab5543</t>
+          <t>https://www.indeed.com/viewjob?jk=17d4577fc7f8f41d</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer AI Native Delivery</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mirantis</t>
+          <t>Taazaa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hudson, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca39720d41d00c5c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0e3e98bb626a4a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer 2</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Stellar Health</t>
+          <t>Mirantis</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094c3e48e41b0fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=ca39720d41d00c5c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Solutions Architect – Data Analytics (Remote)</t>
+          <t>Senior Software Engineer 2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Stellar Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Databricks Lakehouse, Power BI, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL, MySQL, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25bb148408c57615</t>
+          <t>https://www.indeed.com/viewjob?jk=094c3e48e41b0fa1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5141a554cf1e2b91</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d64b090a5428a5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d64b090a5428a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5141a554cf1e2b91</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Business Analyst - Data Intelligence</t>
+          <t>Systems Programmer Analyst l - Java</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Brown Brothers Harriman</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Kafka, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d035d7c47f5688b5</t>
+          <t>https://www.indeed.com/viewjob?jk=94250490a5dea702</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
+          <t>Software Developer Cloud &amp; Distributed Systems</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LexisNexis Reed Tech</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Horsham, PA, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Cassandra, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ef43c8ccb7678a</t>
+          <t>https://www.indeed.com/viewjob?jk=9407487c3afcb12c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Analyst - Data Intelligence</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637d2d6e8ea9d1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=d035d7c47f5688b5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=345c319d29f5fb24</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e39d63930b7f2b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Systems Programmer Analyst l - Java</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Brown Brothers Harriman</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94250490a5dea702</t>
+          <t>https://www.indeed.com/viewjob?jk=a0d555ebdaf6f923</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Developer Cloud &amp; Distributed Systems</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Cassandra, ETL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9407487c3afcb12c</t>
+          <t>https://www.indeed.com/viewjob?jk=92d93d5620e8215a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TBC Corporation</t>
+          <t>Vitol</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, Dimensional Modeling, dbt, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2057a1a27d77eb5f</t>
+          <t>https://www.indeed.com/viewjob?jk=56d3d306f01ceffa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Crane Aerospace &amp; Electronics</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lynnwood, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Oracle, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, DataOps, MLOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df8e9130941aedc7</t>
+          <t>https://www.indeed.com/viewjob?jk=85a75a447f402d78</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Engineer II- AWS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Eventus WholeHealth</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pittsford, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cce58f883c3524b4</t>
+          <t>https://www.indeed.com/viewjob?jk=ad1ed377aab2a771</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Dynamics 365 - Power Platform Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AHU Technologies</t>
+          <t>Crane Aerospace &amp; Electronics</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Lynnwood, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Oracle, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a44cb65cdf117f8c</t>
+          <t>https://www.indeed.com/viewjob?jk=df8e9130941aedc7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>P3+Uplift</t>
+          <t>TBC Corporation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, MySQL, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58d1e81b36b332b5</t>
+          <t>https://www.indeed.com/viewjob?jk=2057a1a27d77eb5f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CFSA Senior Developer D365 Power Platform Azure</t>
+          <t>Software Data Engineering Intern</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Collaboredge</t>
+          <t>Innovation Associates, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a56b6f1122d847a</t>
+          <t>https://www.indeed.com/viewjob?jk=2b6baf999dcc46c5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Software Engineer Azure &amp; Microsoft Cloud</t>
+          <t>Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Leggett &amp; Platt</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bdf03283a9a5d27</t>
+          <t>https://www.indeed.com/viewjob?jk=94f038028488e551</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>P3+Uplift</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, Scala, MySQL, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d4584624626366</t>
+          <t>https://www.indeed.com/viewjob?jk=58d1e81b36b332b5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>IT Architect 5 TX - Enterprise Data &amp; Analytics - FT - Days</t>
+          <t>CFSA Senior Developer D365 Power Platform Azure</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>UC Irvine Health</t>
+          <t>Collaboredge</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Azure, Databricks, GCP, Snowflake, Oracle, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87e85e74388cdd06</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56b6f1122d847a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Technology Business Engineer</t>
+          <t>Senior Dynamics 365 - Power Platform Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ochsner Health</t>
+          <t>AHU Technologies</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jefferson, LA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e95b750693e2318f</t>
+          <t>https://www.indeed.com/viewjob?jk=a44cb65cdf117f8c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Platform Administration Architect</t>
+          <t>Sr Software Engineer Azure &amp; Microsoft Cloud</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wesco</t>
+          <t>Leggett &amp; Platt</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, CI/CD, Azure DevOps</t>
+          <t>Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS, Git, Azure Monitor</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d1276474c632f42</t>
+          <t>https://www.indeed.com/viewjob?jk=7bdf03283a9a5d27</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Application Security Engineer</t>
+          <t>Software Engineer III- Eng</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>REPAY</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4be196fbc9a16bc</t>
+          <t>https://www.indeed.com/viewjob?jk=13debf145d12cdc7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Fullstack Engineer</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Horizon Media, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, Docker</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, IAM, Scala, PostgreSQL, DynamoDB, CI/CD, CloudWatch</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e34e091d0140c14</t>
+          <t>https://www.indeed.com/viewjob?jk=75d4584624626366</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cybersecurity Software Engineer II | ML &amp; AI (Remote)</t>
+          <t>IT Architect 5 TX - Enterprise Data &amp; Analytics - FT - Days</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>UC Irvine Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,15 +3251,190 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>AWS, EMR, Athena, RDS, Azure, Databricks, GCP, Snowflake, Oracle, ETL</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87e85e74388cdd06</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Technology Business Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Ochsner Health</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Jefferson, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e95b750693e2318f</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Application Security Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>REPAY</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4be196fbc9a16bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Data Platform Administration Architect</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Wesco</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d1276474c632f42</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Horizon Media, Inc.</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, Docker</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e34e091d0140c14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Cybersecurity Software Engineer II | ML &amp; AI (Remote)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7243ca669e449c88</t>
         </is>
